--- a/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB_BOM_Main-Controller-Board-v1.1.0.xlsx
+++ b/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB_BOM_Main-Controller-Board-v1.1.0.xlsx
@@ -369,10 +369,10 @@
     <t>C5123515</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>SMB</t>
+  </si>
+  <si>
+    <t>C2934078</t>
   </si>
 </sst>
 </file>
@@ -989,7 +989,7 @@
         <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>94</v>
@@ -1216,7 +1216,7 @@
         <v>80</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
